--- a/lugat.xlsx
+++ b/lugat.xlsx
@@ -7,7 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lugat" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Umumiy" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sayohat" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ish" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -571,46 +573,38 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>book</t>
+          <t>tea</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>kitob</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>ot (noun)</t>
-        </is>
-      </c>
+          <t>choy</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>book</t>
+          <t>sweet</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>bron qilmoq</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>fe'l (verb)</t>
-        </is>
-      </c>
+          <t>shirin</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>beautiful</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>uy</t>
+          <t>go'zal</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
@@ -618,12 +612,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>friend</t>
+          <t>city</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>do'st</t>
+          <t>shahar</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
@@ -631,12 +625,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>family</t>
+          <t>street</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>oila</t>
+          <t>ko'cha</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -644,38 +638,46 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>school</t>
+          <t>book</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>maktab</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>kitob</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ot (noun)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>teacher</t>
+          <t>book</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>o'qituvchi</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
+          <t>bron qilmoq</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>fe'l (verb)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>student</t>
+          <t>house</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>talaba</t>
+          <t>uy</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
@@ -683,12 +685,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>friend</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>shahar</t>
+          <t>do'st</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
@@ -696,12 +698,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>street</t>
+          <t>family</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ko'cha</t>
+          <t>oila</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
@@ -709,12 +711,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>how are you?</t>
+          <t>school</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>qalaysiz?</t>
+          <t>maktab</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
@@ -722,12 +724,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>my name is</t>
+          <t>teacher</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>mening ismim</t>
+          <t>o'qituvchi</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
@@ -735,12 +737,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>where is</t>
+          <t>student</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>qayerda</t>
+          <t>talaba</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
@@ -748,12 +750,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>how much</t>
+          <t>today</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>qancha</t>
+          <t>bugun</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
@@ -761,12 +763,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>I don't understand</t>
+          <t>tomorrow</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>men tushunmayapman</t>
+          <t>ertaga</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
@@ -774,12 +776,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>help</t>
+          <t>yesterday</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>yordam</t>
+          <t>kecha</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
@@ -787,12 +789,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>help</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ochiq</t>
+          <t>yordam</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
@@ -800,12 +802,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>open</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>yopiq</t>
+          <t>ochiq</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
@@ -813,41 +815,295 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>today</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>bugun</t>
+          <t>yopiq</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>tomorrow</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>ertaga</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>yesterday</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>kecha</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>O'zbek</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Izoh</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>airport</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>aeroport</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ticket</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>chipta</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>passport</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>pasport</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>mehmonxona</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>where is</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>qayerda</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>how much</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>qancha</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>I don't understand</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>men tushunmayapman</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>how are you?</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>qalaysiz?</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>train</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>poyezd</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>xarita</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>O'zbek</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Izoh</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>meeting</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>yig'ilish</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>deadline</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>muddat</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>salary</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>maosh</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>manager</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>menejer</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>contract</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>shartnoma</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>report</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>hisobot</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
